--- a/data/EEZ_262/EEZ_262.xlsx
+++ b/data/EEZ_262/EEZ_262.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -500,829 +520,860 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1950-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>66</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1950-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>catch_tonnes</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_tonnes</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ppr_over_npp_percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B13" t="n">
-        <v>326.828</v>
-      </c>
-      <c r="C13" t="n">
-        <v>273087.531</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B14" t="n">
-        <v>334.573</v>
-      </c>
-      <c r="C14" t="n">
-        <v>279995.239</v>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>catch_tonnes</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_tonnes</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>ppr_over_npp_percent</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B15" t="n">
-        <v>349.843</v>
+        <v>326.828</v>
       </c>
       <c r="C15" t="n">
-        <v>288336.087</v>
+        <v>273087.531</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B16" t="n">
-        <v>356.995</v>
+        <v>334.573</v>
       </c>
       <c r="C16" t="n">
-        <v>295129.942</v>
+        <v>279995.239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B17" t="n">
-        <v>362.924</v>
+        <v>349.843</v>
       </c>
       <c r="C17" t="n">
-        <v>301690.836</v>
+        <v>288336.087</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B18" t="n">
-        <v>389.747</v>
+        <v>356.995</v>
       </c>
       <c r="C18" t="n">
-        <v>312232.983</v>
+        <v>295129.942</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B19" t="n">
-        <v>362.781</v>
+        <v>362.924</v>
       </c>
       <c r="C19" t="n">
-        <v>312525.816</v>
+        <v>301690.836</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B20" t="n">
-        <v>371.962</v>
+        <v>389.747</v>
       </c>
       <c r="C20" t="n">
-        <v>319707.173</v>
+        <v>312232.983</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B21" t="n">
-        <v>369.562</v>
+        <v>362.781</v>
       </c>
       <c r="C21" t="n">
-        <v>324681.72</v>
+        <v>312525.816</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B22" t="n">
-        <v>389.237</v>
+        <v>371.962</v>
       </c>
       <c r="C22" t="n">
-        <v>333862.543</v>
+        <v>319707.173</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B23" t="n">
-        <v>389.181</v>
+        <v>369.562</v>
       </c>
       <c r="C23" t="n">
-        <v>339283.795</v>
+        <v>324681.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B24" t="n">
-        <v>386.606</v>
+        <v>389.237</v>
       </c>
       <c r="C24" t="n">
-        <v>344225.111</v>
+        <v>333862.543</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B25" t="n">
-        <v>399.421</v>
+        <v>389.181</v>
       </c>
       <c r="C25" t="n">
-        <v>352101.419</v>
+        <v>339283.795</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B26" t="n">
-        <v>400.872</v>
+        <v>386.606</v>
       </c>
       <c r="C26" t="n">
-        <v>358454.62</v>
+        <v>344225.111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B27" t="n">
-        <v>412.218</v>
+        <v>399.421</v>
       </c>
       <c r="C27" t="n">
-        <v>365449.896</v>
+        <v>352101.419</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B28" t="n">
-        <v>420.348</v>
+        <v>400.872</v>
       </c>
       <c r="C28" t="n">
-        <v>377320.838</v>
+        <v>358454.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B29" t="n">
-        <v>478.855</v>
+        <v>412.218</v>
       </c>
       <c r="C29" t="n">
-        <v>393764.222</v>
+        <v>365449.896</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B30" t="n">
-        <v>477.342</v>
+        <v>420.348</v>
       </c>
       <c r="C30" t="n">
-        <v>399967.321</v>
+        <v>377320.838</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B31" t="n">
-        <v>457.186</v>
+        <v>478.855</v>
       </c>
       <c r="C31" t="n">
-        <v>410071.458</v>
+        <v>393764.222</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B32" t="n">
-        <v>480.864</v>
+        <v>477.342</v>
       </c>
       <c r="C32" t="n">
-        <v>432070.206</v>
+        <v>399967.321</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B33" t="n">
-        <v>522.71</v>
+        <v>457.186</v>
       </c>
       <c r="C33" t="n">
-        <v>452617.828</v>
+        <v>410071.458</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B34" t="n">
-        <v>507.315</v>
+        <v>480.864</v>
       </c>
       <c r="C34" t="n">
-        <v>463100.837</v>
+        <v>432070.206</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B35" t="n">
-        <v>560.919</v>
+        <v>522.71</v>
       </c>
       <c r="C35" t="n">
-        <v>488231.911</v>
+        <v>452617.828</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B36" t="n">
-        <v>683.485</v>
+        <v>507.315</v>
       </c>
       <c r="C36" t="n">
-        <v>531763.9449999999</v>
+        <v>463100.837</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B37" t="n">
-        <v>777.109</v>
+        <v>560.919</v>
       </c>
       <c r="C37" t="n">
-        <v>566914.58</v>
+        <v>488231.911</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B38" t="n">
-        <v>723.251</v>
+        <v>683.485</v>
       </c>
       <c r="C38" t="n">
-        <v>562118.765</v>
+        <v>531763.9449999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B39" t="n">
-        <v>840.769</v>
+        <v>777.109</v>
       </c>
       <c r="C39" t="n">
-        <v>598084.9570000001</v>
+        <v>566914.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B40" t="n">
-        <v>945.7329999999999</v>
+        <v>723.251</v>
       </c>
       <c r="C40" t="n">
-        <v>640502.081</v>
+        <v>562118.765</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B41" t="n">
-        <v>872.025</v>
+        <v>840.769</v>
       </c>
       <c r="C41" t="n">
-        <v>583358.544</v>
+        <v>598084.9570000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B42" t="n">
-        <v>1254.065</v>
+        <v>945.7329999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>762562.983</v>
+        <v>640502.081</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B43" t="n">
-        <v>1423.366</v>
+        <v>872.025</v>
       </c>
       <c r="C43" t="n">
-        <v>920115.019</v>
+        <v>583358.544</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B44" t="n">
-        <v>2164.326</v>
+        <v>1254.065</v>
       </c>
       <c r="C44" t="n">
-        <v>1216220.638</v>
+        <v>762562.983</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B45" t="n">
-        <v>1246.178</v>
+        <v>1423.366</v>
       </c>
       <c r="C45" t="n">
-        <v>1072549.535</v>
+        <v>920115.019</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B46" t="n">
-        <v>1425.794</v>
+        <v>2164.326</v>
       </c>
       <c r="C46" t="n">
-        <v>1093452.236</v>
+        <v>1216220.638</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B47" t="n">
-        <v>1627.165</v>
+        <v>1246.178</v>
       </c>
       <c r="C47" t="n">
-        <v>1425881.625</v>
+        <v>1072549.535</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B48" t="n">
-        <v>1600.961</v>
+        <v>1425.794</v>
       </c>
       <c r="C48" t="n">
-        <v>1207433.183</v>
+        <v>1093452.236</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B49" t="n">
-        <v>2080.674</v>
+        <v>1627.165</v>
       </c>
       <c r="C49" t="n">
-        <v>1881445.095</v>
+        <v>1425881.625</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B50" t="n">
-        <v>2256.496</v>
+        <v>1600.961</v>
       </c>
       <c r="C50" t="n">
-        <v>1647134.743</v>
+        <v>1207433.183</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="B51" t="n">
-        <v>2516.465</v>
+        <v>2080.674</v>
       </c>
       <c r="C51" t="n">
-        <v>1598513.81</v>
+        <v>1881445.095</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="B52" t="n">
-        <v>2104.452</v>
+        <v>2256.496</v>
       </c>
       <c r="C52" t="n">
-        <v>1551755.763</v>
+        <v>1647134.743</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B53" t="n">
-        <v>2575.024</v>
+        <v>2516.465</v>
       </c>
       <c r="C53" t="n">
-        <v>2263843.305</v>
+        <v>1598513.81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B54" t="n">
-        <v>2098.204</v>
+        <v>2104.452</v>
       </c>
       <c r="C54" t="n">
-        <v>1957005.484</v>
+        <v>1551755.763</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="B55" t="n">
-        <v>1116.042</v>
+        <v>2575.024</v>
       </c>
       <c r="C55" t="n">
-        <v>968582.499</v>
+        <v>2263843.305</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="B56" t="n">
-        <v>772.737</v>
+        <v>2098.204</v>
       </c>
       <c r="C56" t="n">
-        <v>598112.6580000001</v>
+        <v>1957005.484</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="B57" t="n">
-        <v>1157.804</v>
+        <v>1116.042</v>
       </c>
       <c r="C57" t="n">
-        <v>987596.992</v>
+        <v>968582.499</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="B58" t="n">
-        <v>1506.811</v>
+        <v>772.737</v>
       </c>
       <c r="C58" t="n">
-        <v>1180657.575</v>
+        <v>598112.6580000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B59" t="n">
-        <v>1573.96</v>
+        <v>1157.804</v>
       </c>
       <c r="C59" t="n">
-        <v>1177009.061</v>
+        <v>987596.992</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="B60" t="n">
-        <v>2282.605</v>
+        <v>1506.811</v>
       </c>
       <c r="C60" t="n">
-        <v>1764869.882</v>
+        <v>1180657.575</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="B61" t="n">
-        <v>2374.662</v>
+        <v>1573.96</v>
       </c>
       <c r="C61" t="n">
-        <v>1787470.274</v>
+        <v>1177009.061</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B62" t="n">
-        <v>2419.649</v>
+        <v>2282.605</v>
       </c>
       <c r="C62" t="n">
-        <v>1847327.256</v>
+        <v>1764869.882</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B63" t="n">
-        <v>2386.289</v>
+        <v>2374.662</v>
       </c>
       <c r="C63" t="n">
-        <v>1812258.888</v>
+        <v>1787470.274</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B64" t="n">
-        <v>2481.436</v>
+        <v>2419.649</v>
       </c>
       <c r="C64" t="n">
-        <v>1885447.765</v>
+        <v>1847327.256</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B65" t="n">
-        <v>2575.22</v>
+        <v>2386.289</v>
       </c>
       <c r="C65" t="n">
-        <v>1999363.867</v>
+        <v>1812258.888</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B66" t="n">
-        <v>2684.139</v>
+        <v>2481.436</v>
       </c>
       <c r="C66" t="n">
-        <v>2015304.02</v>
+        <v>1885447.765</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B67" t="n">
-        <v>2918.031</v>
+        <v>2575.22</v>
       </c>
       <c r="C67" t="n">
-        <v>2134045.427</v>
+        <v>1999363.867</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B68" t="n">
-        <v>4599.396</v>
+        <v>2684.139</v>
       </c>
       <c r="C68" t="n">
-        <v>3268099.201</v>
+        <v>2015304.02</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B69" t="n">
-        <v>4005.386</v>
+        <v>2918.031</v>
       </c>
       <c r="C69" t="n">
-        <v>4063932.674</v>
+        <v>2134045.427</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B70" t="n">
-        <v>3562.327</v>
+        <v>4599.396</v>
       </c>
       <c r="C70" t="n">
-        <v>3824553.707</v>
+        <v>3268099.201</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B71" t="n">
-        <v>3245.62</v>
+        <v>4005.386</v>
       </c>
       <c r="C71" t="n">
-        <v>3530744.938</v>
+        <v>4063932.674</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B72" t="n">
-        <v>2971.291</v>
+        <v>3562.327</v>
       </c>
       <c r="C72" t="n">
-        <v>2730301.688</v>
+        <v>3824553.707</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B73" t="n">
-        <v>4775.745</v>
+        <v>3245.62</v>
       </c>
       <c r="C73" t="n">
-        <v>4382696.551</v>
+        <v>3530744.938</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B74" t="n">
-        <v>2988.837</v>
+        <v>2971.291</v>
       </c>
       <c r="C74" t="n">
-        <v>3555070.965</v>
+        <v>2730301.688</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B75" t="n">
-        <v>3657.02</v>
+        <v>4775.745</v>
       </c>
       <c r="C75" t="n">
-        <v>4315643.296</v>
+        <v>4382696.551</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B76" t="n">
-        <v>2861.373</v>
+        <v>2988.837</v>
       </c>
       <c r="C76" t="n">
-        <v>3296228.178</v>
+        <v>3555070.965</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B77" t="n">
-        <v>3822.835</v>
+        <v>3657.02</v>
       </c>
       <c r="C77" t="n">
-        <v>4442527.741</v>
+        <v>4315643.296</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B78" t="n">
-        <v>3266.043</v>
+        <v>2861.373</v>
       </c>
       <c r="C78" t="n">
-        <v>3949593.098</v>
+        <v>3296228.178</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B79" t="n">
-        <v>3828.86</v>
+        <v>3822.835</v>
       </c>
       <c r="C79" t="n">
-        <v>4731090.824</v>
+        <v>4442527.741</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B80" t="n">
-        <v>3695.038</v>
+        <v>3266.043</v>
       </c>
       <c r="C80" t="n">
-        <v>4523691.619</v>
+        <v>3949593.098</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B81" t="n">
-        <v>3871.038</v>
+        <v>3828.86</v>
       </c>
       <c r="C81" t="n">
-        <v>4658455.592</v>
+        <v>4731090.824</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B82" t="n">
-        <v>3605.054</v>
+        <v>3695.038</v>
       </c>
       <c r="C82" t="n">
-        <v>6543782.708</v>
+        <v>4523691.619</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3871.038</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4658455.592</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3605.054</v>
+      </c>
+      <c r="C84" t="n">
+        <v>6543782.708</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>PPR/NPP is blank because no NPP estimate exists for this ecosystem.</t>
         </is>
@@ -1439,355 +1490,215 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AD1" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AE1" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AF1" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AG1" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AH1" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AI1" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AJ1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AK1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AL1" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AM1" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AN1" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AO1" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AP1" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AQ1" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AR1" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AS1" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AT1" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AU1" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AV1" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AW1" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AX1" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AY1" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AZ1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="BA1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="BB1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BC1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BD1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BE1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BF1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BG1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BH1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BI1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BJ1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BK1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BL1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BM1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BN1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BO1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BP1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BQ1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BR1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BS1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BT1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BU1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BV1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1951</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1952</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>1957</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1958</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>1959</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>1960</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>1962</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>1963</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>1964</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>1965</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>1966</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>1967</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>1968</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>1969</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>1970</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>1971</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>1972</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AD1" s="2" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AE1" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AF1" s="2" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AG1" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AH1" s="2" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AI1" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AK1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AL1" s="2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AM1" s="2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AN1" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AX1" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AY1" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AZ1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="BA1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="BB1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BC1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BD1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BE1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BF1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BG1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BH1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BI1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BJ1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BK1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BL1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BM1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BN1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BO1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BP1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BQ1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BR1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BS1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BT1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BU1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BV1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -17707,6 +17618,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17885,355 +18035,215 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="AZ4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="BA4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="BI4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="BJ4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="BK4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="BL4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="BM4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="BN4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="BO4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="BP4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="BQ4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="BR4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="BS4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="BT4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1953</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1954</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1955</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1957</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1959</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>1963</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1964</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>1965</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>1966</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1967</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1969</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1970</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>1972</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AC4" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>1979</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AL4" s="3" t="n">
+        <v>1985</v>
+      </c>
+      <c r="AM4" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="AN4" s="3" t="n">
+        <v>1987</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AR4" s="3" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AS4" s="3" t="n">
+        <v>1992</v>
+      </c>
+      <c r="AT4" s="3" t="n">
+        <v>1993</v>
+      </c>
+      <c r="AU4" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AV4" s="3" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AW4" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="AX4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AY4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="AZ4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="BA4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BB4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="BC4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="BD4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="BE4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="BF4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="BG4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="BS4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="BT4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -27261,7 +27271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/EEZ_262/EEZ_262.xlsx
+++ b/data/EEZ_262/EEZ_262.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$73</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1133,6 +1136,9 @@
       <c r="C63" t="n">
         <v>1787470.274</v>
       </c>
+      <c r="D63" t="n">
+        <v>4.4737</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1144,6 +1150,9 @@
       <c r="C64" t="n">
         <v>1847327.256</v>
       </c>
+      <c r="D64" t="n">
+        <v>4.7998</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1155,6 +1164,9 @@
       <c r="C65" t="n">
         <v>1812258.888</v>
       </c>
+      <c r="D65" t="n">
+        <v>4.9958</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1166,6 +1178,9 @@
       <c r="C66" t="n">
         <v>1885447.765</v>
       </c>
+      <c r="D66" t="n">
+        <v>5.1919</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1177,6 +1192,9 @@
       <c r="C67" t="n">
         <v>1999363.867</v>
       </c>
+      <c r="D67" t="n">
+        <v>5.5551</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1188,6 +1206,9 @@
       <c r="C68" t="n">
         <v>2015304.02</v>
       </c>
+      <c r="D68" t="n">
+        <v>6.4187</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1199,6 +1220,9 @@
       <c r="C69" t="n">
         <v>2134045.427</v>
       </c>
+      <c r="D69" t="n">
+        <v>6.2032</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1210,6 +1234,9 @@
       <c r="C70" t="n">
         <v>3268099.201</v>
       </c>
+      <c r="D70" t="n">
+        <v>8.4251</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1221,6 +1248,9 @@
       <c r="C71" t="n">
         <v>4063932.674</v>
       </c>
+      <c r="D71" t="n">
+        <v>11.9724</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1232,6 +1262,9 @@
       <c r="C72" t="n">
         <v>3824553.707</v>
       </c>
+      <c r="D72" t="n">
+        <v>13.5362</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1243,6 +1276,9 @@
       <c r="C73" t="n">
         <v>3530744.938</v>
       </c>
+      <c r="D73" t="n">
+        <v>13.4247</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1254,6 +1290,9 @@
       <c r="C74" t="n">
         <v>2730301.688</v>
       </c>
+      <c r="D74" t="n">
+        <v>10.2725</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1265,6 +1304,9 @@
       <c r="C75" t="n">
         <v>4382696.551</v>
       </c>
+      <c r="D75" t="n">
+        <v>14.2468</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1276,6 +1318,9 @@
       <c r="C76" t="n">
         <v>3555070.965</v>
       </c>
+      <c r="D76" t="n">
+        <v>11.1096</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1287,6 +1332,9 @@
       <c r="C77" t="n">
         <v>4315643.296</v>
       </c>
+      <c r="D77" t="n">
+        <v>13.9292</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1298,6 +1346,9 @@
       <c r="C78" t="n">
         <v>3296228.178</v>
       </c>
+      <c r="D78" t="n">
+        <v>11.6289</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1309,6 +1360,9 @@
       <c r="C79" t="n">
         <v>4442527.741</v>
       </c>
+      <c r="D79" t="n">
+        <v>15.0565</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1320,6 +1374,9 @@
       <c r="C80" t="n">
         <v>3949593.098</v>
       </c>
+      <c r="D80" t="n">
+        <v>16.0355</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1331,6 +1388,9 @@
       <c r="C81" t="n">
         <v>4731090.824</v>
       </c>
+      <c r="D81" t="n">
+        <v>16.1541</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1342,6 +1402,9 @@
       <c r="C82" t="n">
         <v>4523691.619</v>
       </c>
+      <c r="D82" t="n">
+        <v>13.8313</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1353,6 +1416,9 @@
       <c r="C83" t="n">
         <v>4658455.592</v>
       </c>
+      <c r="D83" t="n">
+        <v>13.5719</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1364,22 +1430,2282 @@
       <c r="C84" t="n">
         <v>6543782.708</v>
       </c>
+      <c r="D84" t="n">
+        <v>17.4626</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>PPR/NPP is blank because no NPP estimate exists for this ecosystem.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1950</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1951</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1952</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1953</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1954</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1955</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1956</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1957</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1958</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1959</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1960</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1961</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1962</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1963</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1964</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1965</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1966</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1967</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1969</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1970</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1971</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1972</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1973</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1974</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1975</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1977</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1978</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1979</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1983</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1984</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1985</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1986</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1987</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1988</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1989</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1990</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1991</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1992</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1993</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1994</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1995</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1996</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4439422.976759179</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4439422.976759179</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4439422.976759179</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4439422.976759179</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/1998/848d73be4edbdf39/provenance.json</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4276419.493540788</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4276419.493540788</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4276419.493540788</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4276419.493540788</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/1999/7c2a53b46a02284b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4030622.357523108</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4030622.357523108</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4030622.357523108</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4030622.357523108</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2000/4061cb7fd4278b03/provenance.json</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4034991.889125098</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4034991.889125098</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4034991.889125098</v>
+      </c>
+      <c r="I55" t="n">
+        <v>4034991.889125098</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2001/af4237f96f450f68/provenance.json</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3999022.02140608</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3999022.02140608</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3999022.02140608</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3999022.02140608</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2002/cb18d36c3928416f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4676615.574982392</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2876505.577615608</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5868857.338853435</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3488593.552236244</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1682814.900070306</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3488593.552236244</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1682814.900070306</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5868857.338853435</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2003/e3b8e4aba049aba8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>5</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5316315.669185652</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2391772.908568311</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4674518.106700004</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3822496.816349561</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1740578.307039878</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3822496.816349561</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1740578.307039878</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5316315.669185652</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2004/1578102eb802e4fd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4656328.149766824</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2388259.198442893</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4755788.762891523</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4309982.360312809</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1885630.738895721</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4309982.360312809</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1885630.738895721</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4755788.762891523</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2005/789df515cc84d5eb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>5</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4368635.099584574</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2382443.276593039</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4675707.262008072</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3771589.456809853</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1614499.230294605</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3771589.456809853</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1614499.230294605</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4675707.262008072</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2006/f986afa7dea50b92/provenance.json</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>5</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4786466.257091132</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2979252.429628563</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6684409.411485095</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3139371.254792978</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1484546.510316507</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3139371.254792978</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1484546.510316507</v>
+      </c>
+      <c r="I61" t="n">
+        <v>6684409.411485095</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2007/8f3c65d96b0e1768/provenance.json</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>5</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3717832.038006364</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1764741.297598642</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3113420.185354984</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2922266.710042869</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1564048.113379671</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2922266.710042869</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1564048.113379671</v>
+      </c>
+      <c r="I62" t="n">
+        <v>3717832.038006364</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2008/f78aee8d26ee4e4e/provenance.json</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3681855.767750013</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1911901.750350915</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3465372.729944677</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2953195.689001393</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1450781.738933558</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2953195.689001393</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1450781.738933558</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3681855.767750013</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2009/6fada420a161df7f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>5</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3917657.224838354</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1976785.899896672</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3843142.434895496</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3418068.290443236</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1076816.923814943</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3418068.290443236</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1076816.923814943</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3917657.224838354</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2010/9faaa1063acdd9a4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>5</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4167845.621585385</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2690421.925606128</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5260112.536536617</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3555547.148285683</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1313851.497706117</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3555547.148285683</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1313851.497706117</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5260112.536536617</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2011/cda796c56dcdcd17/provenance.json</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3442514.943415036</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2125286.192995175</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3976539.659564271</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3738364.780339673</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1234522.770045226</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3442514.943415036</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1234522.770045226</v>
+      </c>
+      <c r="I66" t="n">
+        <v>3976539.659564271</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2012/c7b676f92b834ce4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>5</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3267295.839268721</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1874537.245792888</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3544404.531482445</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3149472.313981119</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1236513.461979966</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3149472.313981119</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1236513.461979966</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3544404.531482445</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2013/636a6761243c02fa/provenance.json</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>5</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3278403.333415076</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1912687.116505269</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3664528.381772012</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3413263.448045497</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1557623.541526506</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3278403.333415076</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1557623.541526506</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3664528.381772012</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2014/f2e604b8075f7f7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2736708.58711647</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1790963.868044139</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3450001.653850772</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3264208.83132256</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1370551.193177068</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2736708.58711647</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1370551.193177068</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3450001.653850772</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2015/f29fd1ff26db87ab/provenance.json</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>5</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3459311.875038947</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1930249.813144215</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3728456.525950035</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3254143.865550831</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1292092.874068029</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3254143.865550831</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1292092.874068029</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3728456.525950035</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2016/66abb99f6b269024/provenance.json</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3698660.204136967</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1908238.950642793</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3727440.372808027</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3634012.59351855</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1505994.207247985</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3634012.59351855</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1505994.207247985</v>
+      </c>
+      <c r="I71" t="n">
+        <v>3727440.372808027</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2017/9efa693e10f193e3/provenance.json</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3813800.017215504</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2136724.766968817</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4057441.430581706</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3947382.844345175</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1565228.829294638</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3813800.017215504</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1565228.829294638</v>
+      </c>
+      <c r="I72" t="n">
+        <v>4057441.430581706</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2018/9bc98aadb26d4272/provenance.json</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>5</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B73" t="n">
+        <v>4163672.465925097</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2436959.187606139</v>
+      </c>
+      <c r="D73" t="n">
+        <v>5207043.593717531</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4193067.871353164</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1213198.064269265</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4163672.465925097</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1213198.064269265</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5207043.593717531</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/regional_expansion/years/2019/e1437b825b558fb7/provenance.json</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17024,591 +19350,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for EEZ_262</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Scomberomorus commerson</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Caranx sexfasciatus</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Euthynnus affinis</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Thunnus tonggol</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sphyraena jello</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Seriola dumerili</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3162.27766</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sphyraena barracuda</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3090.295433</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Scomberoides commersonnianus</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3019.95172</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Istiophoridae</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3019.95172</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Trichiurus lepturus</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2630.267992</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Thunnus albacares</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2570.395783</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sphyraenidae</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2511.886432</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sphyraena</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2511.886432</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Scomberomorus</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2238.721139</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Flavocaranx bajad</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1995.262315</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Lutjanus bohar</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1862.087137</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Scombridae</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1819.700859</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Carcharhinidae</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1737.800829</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Caranx ignobilis</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1659.586907</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Carangidae</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1122.018454</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Elasmobranchii</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1122.018454</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Lutjanidae</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1047.128548</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Epinephelus chlorostigma</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="C27" t="n">
-        <v>977.237221</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Epinephelus polyphekadion</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="C28" t="n">
-        <v>977.237221</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Serranidae</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="C29" t="n">
-        <v>954.992586</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Rachycentron canadum</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="C30" t="n">
-        <v>912.010839</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Pristipomoides</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="C31" t="n">
-        <v>812.830516</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Epinephelus</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="C32" t="n">
-        <v>691.830971</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Lethrinus</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="C33" t="n">
-        <v>562.341325</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Epinephelus areolatus</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="C34" t="n">
-        <v>549.540874</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C35" t="n">
-        <v>407.380278</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Lethrinidae</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="C36" t="n">
-        <v>389.045145</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Lutjanus argentimaculatus</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="C37" t="n">
-        <v>380.189396</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Panulirus versicolor</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="C38" t="n">
-        <v>371.535229</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Ariidae</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="C39" t="n">
-        <v>301.995172</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Lethrinus mahsena</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="C40" t="n">
-        <v>269.15348</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Marine pelagic fishes not identified</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="C41" t="n">
-        <v>223.872114</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C42" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Marine groundfishes not identified</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C43" t="n">
-        <v>165.958691</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Miscellaneous marine crustaceans</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C44" t="n">
-        <v>50.118723</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Mugilidae</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="C45" t="n">
-        <v>33.884416</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -17623,43 +19381,591 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for EEZ_262</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Scomberomorus commerson</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Caranx sexfasciatus</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Euthynnus affinis</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thunnus tonggol</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sphyraena jello</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Seriola dumerili</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3162.27766</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sphyraena barracuda</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3090.295433</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Scomberoides commersonnianus</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3019.95172</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Istiophoridae</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3019.95172</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trichiurus lepturus</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2630.267992</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thunnus albacares</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2570.395783</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sphyraenidae</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2511.886432</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sphyraena</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2511.886432</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Scomberomorus</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2238.721139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Flavocaranx bajad</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1995.262315</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Lutjanus bohar</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1862.087137</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Scombridae</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1819.700859</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Carcharhinidae</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1737.800829</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Caranx ignobilis</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1659.586907</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Carangidae</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1122.018454</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Elasmobranchii</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1122.018454</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lutjanidae</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1047.128548</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Epinephelus chlorostigma</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="C27" t="n">
+        <v>977.237221</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Epinephelus polyphekadion</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="C28" t="n">
+        <v>977.237221</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Serranidae</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="C29" t="n">
+        <v>954.992586</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Rachycentron canadum</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="C30" t="n">
+        <v>912.010839</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Pristipomoides</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C31" t="n">
+        <v>812.830516</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Epinephelus</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="C32" t="n">
+        <v>691.830971</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Lethrinus</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="C33" t="n">
+        <v>562.341325</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Epinephelus areolatus</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="C34" t="n">
+        <v>549.540874</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C35" t="n">
+        <v>407.380278</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Lethrinidae</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="C36" t="n">
+        <v>389.045145</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lutjanus argentimaculatus</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C37" t="n">
+        <v>380.189396</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Panulirus versicolor</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="C38" t="n">
+        <v>371.535229</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ariidae</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="C39" t="n">
+        <v>301.995172</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lethrinus mahsena</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C40" t="n">
+        <v>269.15348</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Marine pelagic fishes not identified</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C41" t="n">
+        <v>223.872114</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C42" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Marine groundfishes not identified</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C43" t="n">
+        <v>165.958691</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Miscellaneous marine crustaceans</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C44" t="n">
+        <v>50.118723</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Mugilidae</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="C45" t="n">
+        <v>33.884416</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -17684,14 +19990,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -17735,14 +20041,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -17771,6 +20077,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17856,7 +20213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27269,32 +29626,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>No net primary production estimate is available for this ecosystem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NPP currently covers LME and High Seas units only, not EEZs.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>